--- a/sh.xlsx
+++ b/sh.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gisco\Desktop\WEB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gisco\Desktop\WEBB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEFAB229-77F8-499C-9186-AC4506832FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{385B496B-6D1B-4369-80E1-63E8A079A591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="302">
   <si>
     <t>REQUEST</t>
   </si>
@@ -899,6 +899,33 @@
   </si>
   <si>
     <t>REQ2600014775</t>
+  </si>
+  <si>
+    <t>PO2600010444</t>
+  </si>
+  <si>
+    <t>COMPRESSOR SCROLL, 3PHASE, MODEL NO. ZP125KCE-TFD-522, (USED) MAKE: COPELAND</t>
+  </si>
+  <si>
+    <t> 10016940</t>
+  </si>
+  <si>
+    <t>COMPRESSOR SCROLL (USED), PART NO: ZP154KCE-TWD550, MAKE: COPELAND</t>
+  </si>
+  <si>
+    <t> 10032514</t>
+  </si>
+  <si>
+    <t>COMPRESSOR SCROLL (USED), MODEL NO. ZP90KCE-TFD-550, LRA-95, 410 GAS, 3PH, MAKE: COPELAND, ORIGIN: THAILAND</t>
+  </si>
+  <si>
+    <t> 10055795</t>
+  </si>
+  <si>
+    <t>COMPRESSOR, MODEL NO. 750EL-128D3, R22, V440, (USED), MAKE: HITACHI</t>
+  </si>
+  <si>
+    <t>REQ2600017807</t>
   </si>
 </sst>
 </file>
@@ -1275,7 +1302,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I170"/>
+  <dimension ref="A1:I178"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.875" customWidth="1"/>
@@ -4871,7 +4898,7 @@
         <v>12</v>
       </c>
       <c r="G124">
-        <f t="shared" ref="G124:G170" si="0">E124*D124</f>
+        <f t="shared" ref="G124:G178" si="0">E124*D124</f>
         <v>1350</v>
       </c>
       <c r="H124" t="s">
@@ -6259,6 +6286,246 @@
       </c>
       <c r="I170" t="s">
         <v>276</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>301</v>
+      </c>
+      <c r="B171" t="s">
+        <v>75</v>
+      </c>
+      <c r="C171" t="s">
+        <v>285</v>
+      </c>
+      <c r="D171">
+        <v>5</v>
+      </c>
+      <c r="E171">
+        <v>225</v>
+      </c>
+      <c r="F171" t="s">
+        <v>12</v>
+      </c>
+      <c r="G171">
+        <f t="shared" si="0"/>
+        <v>1125</v>
+      </c>
+      <c r="H171" t="s">
+        <v>13</v>
+      </c>
+      <c r="I171" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>301</v>
+      </c>
+      <c r="B172" t="s">
+        <v>228</v>
+      </c>
+      <c r="C172" t="s">
+        <v>229</v>
+      </c>
+      <c r="D172">
+        <v>5</v>
+      </c>
+      <c r="E172">
+        <v>225</v>
+      </c>
+      <c r="F172" t="s">
+        <v>12</v>
+      </c>
+      <c r="G172">
+        <f t="shared" si="0"/>
+        <v>1125</v>
+      </c>
+      <c r="H172" t="s">
+        <v>13</v>
+      </c>
+      <c r="I172" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>301</v>
+      </c>
+      <c r="B173" t="s">
+        <v>208</v>
+      </c>
+      <c r="C173" t="s">
+        <v>294</v>
+      </c>
+      <c r="D173">
+        <v>1</v>
+      </c>
+      <c r="E173">
+        <v>1200</v>
+      </c>
+      <c r="F173" t="s">
+        <v>12</v>
+      </c>
+      <c r="G173">
+        <f t="shared" si="0"/>
+        <v>1200</v>
+      </c>
+      <c r="H173" t="s">
+        <v>13</v>
+      </c>
+      <c r="I173" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>301</v>
+      </c>
+      <c r="B174" t="s">
+        <v>79</v>
+      </c>
+      <c r="C174" t="s">
+        <v>80</v>
+      </c>
+      <c r="D174">
+        <v>2</v>
+      </c>
+      <c r="E174">
+        <v>1600</v>
+      </c>
+      <c r="F174" t="s">
+        <v>12</v>
+      </c>
+      <c r="G174">
+        <f t="shared" si="0"/>
+        <v>3200</v>
+      </c>
+      <c r="H174" t="s">
+        <v>13</v>
+      </c>
+      <c r="I174" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>301</v>
+      </c>
+      <c r="B175" t="s">
+        <v>295</v>
+      </c>
+      <c r="C175" t="s">
+        <v>296</v>
+      </c>
+      <c r="D175">
+        <v>2</v>
+      </c>
+      <c r="E175">
+        <v>1600</v>
+      </c>
+      <c r="F175" t="s">
+        <v>12</v>
+      </c>
+      <c r="G175">
+        <f t="shared" si="0"/>
+        <v>3200</v>
+      </c>
+      <c r="H175" t="s">
+        <v>13</v>
+      </c>
+      <c r="I175" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>301</v>
+      </c>
+      <c r="B176" t="s">
+        <v>75</v>
+      </c>
+      <c r="C176" t="s">
+        <v>285</v>
+      </c>
+      <c r="D176">
+        <v>5</v>
+      </c>
+      <c r="E176">
+        <v>225</v>
+      </c>
+      <c r="F176" t="s">
+        <v>12</v>
+      </c>
+      <c r="G176">
+        <f t="shared" si="0"/>
+        <v>1125</v>
+      </c>
+      <c r="H176" t="s">
+        <v>13</v>
+      </c>
+      <c r="I176" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>301</v>
+      </c>
+      <c r="B177" t="s">
+        <v>297</v>
+      </c>
+      <c r="C177" t="s">
+        <v>298</v>
+      </c>
+      <c r="D177">
+        <v>1</v>
+      </c>
+      <c r="E177">
+        <v>1200</v>
+      </c>
+      <c r="F177" t="s">
+        <v>12</v>
+      </c>
+      <c r="G177">
+        <f t="shared" si="0"/>
+        <v>1200</v>
+      </c>
+      <c r="H177" t="s">
+        <v>13</v>
+      </c>
+      <c r="I177" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>301</v>
+      </c>
+      <c r="B178" t="s">
+        <v>299</v>
+      </c>
+      <c r="C178" t="s">
+        <v>300</v>
+      </c>
+      <c r="D178">
+        <v>2</v>
+      </c>
+      <c r="E178">
+        <v>1500</v>
+      </c>
+      <c r="F178" t="s">
+        <v>12</v>
+      </c>
+      <c r="G178">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+      <c r="H178" t="s">
+        <v>13</v>
+      </c>
+      <c r="I178" t="s">
+        <v>293</v>
       </c>
     </row>
   </sheetData>
